--- a/data/administracion_de_tribunales/OP_LEY148FinalEmitidas.xlsx
+++ b/data/administracion_de_tribunales/OP_LEY148FinalEmitidas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF145359-D5D2-4BC1-80FD-9BD0C9B20465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6570534-C6C0-451D-98F1-C40814F22017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="748" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="4" r:id="rId1"/>
@@ -1541,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -1550,81 +1550,107 @@
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
       <c r="D3" s="3">
         <v>3</v>
       </c>
       <c r="E3" s="3">
         <v>3</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9</v>
+      </c>
       <c r="D7" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1635,92 +1661,130 @@
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3">
-        <v>2</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
       <c r="E12" s="3">
-        <v>4</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="B13" s="3">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3">
         <v>3</v>
@@ -1728,7 +1792,9 @@
       <c r="E14" s="3">
         <v>4</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
@@ -1736,23 +1802,23 @@
       </c>
       <c r="B15" s="3">
         <f>SUM(B2:B14)</f>
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" ref="C15:F15" si="0">SUM(C2:C14)</f>
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
